--- a/laboratorios/Sesion02/laboratorioI_Clave.xlsx
+++ b/laboratorios/Sesion02/laboratorioI_Clave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/Docencia/2026/III/Macroeconomía/macroeconomia-200fp/laboratorios/sesion02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB027C-2E1A-4349-9194-CC4B1BF21FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F9B4B0-6F27-8344-9CD7-BE6CAD40FF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="1" r:id="rId1"/>
@@ -1558,7 +1558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1606,32 +1606,37 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1639,14 +1644,15 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1654,14 +1660,8 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1673,9 +1673,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2269,6 +2266,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Índice"/>
@@ -3295,7 +3293,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -3307,7 +3305,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -3317,7 +3315,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="26" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="16"/>
@@ -3335,7 +3333,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="8" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="16"/>
@@ -3348,28 +3346,28 @@
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="26"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="16"/>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="26"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="16"/>
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="16"/>
@@ -3379,7 +3377,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="16"/>
@@ -3389,7 +3387,7 @@
       <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="16"/>
@@ -3399,7 +3397,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16"/>
@@ -3409,7 +3407,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="16"/>
@@ -3419,7 +3417,7 @@
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="16"/>
@@ -3429,7 +3427,7 @@
       <c r="G17" s="16"/>
     </row>
     <row r="19" spans="2:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="16"/>
@@ -3439,11 +3437,11 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="22" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="16"/>
@@ -3451,11 +3449,11 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="22" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16"/>
@@ -3463,11 +3461,11 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="22" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="16"/>
@@ -3475,11 +3473,11 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="28" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="16"/>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="22" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="16"/>
@@ -3487,7 +3485,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="25" spans="2:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="16"/>
@@ -3497,7 +3495,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="27" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="16"/>
@@ -3516,18 +3514,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B5:G6"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B26:G27"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="B23:C23"/>
@@ -3542,6 +3528,18 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:G13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B5:G6"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B8:G8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -3583,7 +3581,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="16"/>
@@ -3595,7 +3593,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -3605,7 +3603,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="16"/>
@@ -3624,19 +3622,19 @@
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="2">
         <v>2013</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="2">
         <v>2019</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="2">
         <v>2020</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3841,7 +3839,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="16"/>
@@ -3885,7 +3883,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="16"/>
@@ -3927,7 +3925,7 @@
       <c r="F28" s="16"/>
     </row>
     <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="17" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="16"/>
@@ -4029,7 +4027,7 @@
       <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="16"/>
@@ -4042,7 +4040,7 @@
       <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -4209,7 +4207,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="21" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="16"/>
@@ -4252,7 +4250,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="17" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="16"/>
@@ -4314,7 +4312,7 @@
       <c r="H34" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B36" s="16"/>
@@ -4428,7 +4426,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>57</v>
       </c>
       <c r="B2" s="16"/>
@@ -4440,7 +4438,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -4450,7 +4448,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="21" t="s">
         <v>58</v>
       </c>
       <c r="B6" s="16"/>
@@ -4468,7 +4466,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="35" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="16"/>
@@ -4498,7 +4496,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="16"/>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <f>B17</f>
         <v>7052.9348650000002</v>
       </c>
@@ -4527,7 +4525,7 @@
         <v>60</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="33" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="16"/>
@@ -4557,20 +4555,20 @@
         <v>60</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="F13" s="35">
+      <c r="F13" s="34">
         <f>B18</f>
         <v>2115.8804595000001</v>
       </c>
       <c r="G13" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="36" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="21" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="16"/>
@@ -4587,11 +4585,11 @@
         <f>Etapa1_Datos!F12</f>
         <v>7052.9348650000002</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="37" t="s">
         <v>72</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="F17" s="35">
+      <c r="F17" s="34">
         <f>B19</f>
         <v>528.97011487500004</v>
       </c>
@@ -4605,7 +4603,7 @@
         <f>B17*B7</f>
         <v>2115.8804595000001</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="37" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="16"/>
@@ -4618,13 +4616,13 @@
         <f>B18*B8</f>
         <v>528.97011487500004</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="37" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="17" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="16"/>
@@ -4689,7 +4687,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="31" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>78</v>
       </c>
       <c r="B31" s="16"/>
@@ -4737,15 +4735,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A32:G35"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A2:H2"/>
@@ -4762,6 +4751,15 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G29"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -4804,7 +4802,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>80</v>
       </c>
       <c r="B2" s="16"/>
@@ -4816,7 +4814,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -4891,7 +4889,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="16"/>
@@ -4917,7 +4915,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="17" t="s">
         <v>91</v>
       </c>
       <c r="B18" s="16"/>
@@ -4982,7 +4980,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="17" t="s">
         <v>92</v>
       </c>
       <c r="B26" s="16"/>
@@ -5077,7 +5075,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="16"/>
@@ -5089,7 +5087,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -5194,7 +5192,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>99</v>
       </c>
       <c r="B31" s="16"/>
@@ -5252,7 +5250,7 @@
       <c r="F37" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="17" t="s">
         <v>100</v>
       </c>
       <c r="B39" s="16"/>
@@ -5340,7 +5338,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>102</v>
       </c>
       <c r="B2" s="16"/>
@@ -5352,7 +5350,7 @@
       <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -5362,7 +5360,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="21" t="s">
         <v>103</v>
       </c>
       <c r="B6" s="16"/>
@@ -5440,7 +5438,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="21" t="s">
         <v>109</v>
       </c>
       <c r="B15" s="16"/>
@@ -5582,7 +5580,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="21" t="s">
         <v>111</v>
       </c>
       <c r="B31" s="16"/>
@@ -5594,7 +5592,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="17" t="s">
         <v>112</v>
       </c>
       <c r="B32" s="16"/>
@@ -5636,7 +5634,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="17" t="s">
         <v>113</v>
       </c>
       <c r="B37" s="16"/>
@@ -5678,7 +5676,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="17" t="s">
         <v>114</v>
       </c>
       <c r="B42" s="16"/>
@@ -5720,7 +5718,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="17" t="s">
         <v>115</v>
       </c>
       <c r="B47" s="16"/>
@@ -5762,7 +5760,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="21" t="s">
         <v>116</v>
       </c>
       <c r="B53" s="16"/>
@@ -5807,14 +5805,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A43:H45"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A48:H50"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A54:H56"/>
@@ -5831,6 +5821,14 @@
     <mergeCell ref="A33:H35"/>
     <mergeCell ref="A38:H40"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A43:H45"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>

--- a/laboratorios/Sesion02/laboratorioI_Clave.xlsx
+++ b/laboratorios/Sesion02/laboratorioI_Clave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/Docencia/2026/III/Macroeconomía/macroeconomia-200fp/laboratorios/sesion02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F9B4B0-6F27-8344-9CD7-BE6CAD40FF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33732E3F-540D-2946-87EE-8122584F82B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="1" r:id="rId1"/>
@@ -52,10 +52,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Celda de entrada: complete con información del Banco de Guatemala o con el dato solicitado.</t>
         </r>
@@ -662,10 +661,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Celda de entrada: complete con información del Banco de Guatemala o con el dato solicitado.</t>
         </r>
@@ -824,10 +822,9 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Supuesto académico del caso ANDAR GT, S.A. Puede modificarse para análisis de sensibilidad.</t>
         </r>
@@ -918,7 +915,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="124">
   <si>
     <t>LABORATORIO DE APLICACIÓN</t>
   </si>
@@ -1282,17 +1279,30 @@
   </si>
   <si>
     <t>2024 p/</t>
+  </si>
+  <si>
+    <t>INGRESO</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Q</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\Q\ #,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,6 +1427,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1471,7 +1488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1554,11 +1571,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1602,15 +1629,15 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1619,24 +1646,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1644,15 +1665,15 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1660,8 +1681,14 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1673,8 +1700,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2191,6 +2222,55 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205153</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>140861</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>448931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1E52ACB-5B81-3399-B7F4-6DEC7771D0DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9798538" y="3175000"/>
+          <a:ext cx="6842554" cy="2217162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2225,7 +2305,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -3281,7 +3361,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -3315,7 +3395,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="16"/>
@@ -3346,24 +3426,24 @@
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="24"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="16"/>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="25"/>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="24"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="16"/>
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -3377,7 +3457,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="16"/>
@@ -3387,7 +3467,7 @@
       <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="26" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="16"/>
@@ -3397,7 +3477,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16"/>
@@ -3407,7 +3487,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="26" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="16"/>
@@ -3417,7 +3497,7 @@
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="26" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="16"/>
@@ -3437,11 +3517,11 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="27" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="16"/>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="23" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="16"/>
@@ -3449,11 +3529,11 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="29" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="16"/>
@@ -3461,11 +3541,11 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="28" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="23" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="16"/>
@@ -3473,11 +3553,11 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="16"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="16"/>
@@ -3495,7 +3575,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="22" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="16"/>
@@ -3514,6 +3594,18 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B5:G6"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B26:G27"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="B23:C23"/>
@@ -3528,18 +3620,6 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:G13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B5:G6"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B8:G8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -3559,17 +3639,20 @@
     <tabColor rgb="FFF97316"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="3" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="16"/>
@@ -3838,7 +3921,7 @@
         <v>7794.133960000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
         <v>37</v>
       </c>
@@ -3848,7 +3931,7 @@
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -3857,7 +3940,7 @@
         <v>7794.133960000001</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -3866,7 +3949,7 @@
         <v>7794.133960000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -3882,7 +3965,7 @@
         <v>Sí</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
@@ -3892,15 +3975,15 @@
       <c r="E24" s="16"/>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
+    <row r="25" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="18"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -3908,7 +3991,7 @@
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -3916,15 +3999,31 @@
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
-    </row>
-    <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N28" s="42">
+        <v>15</v>
+      </c>
+      <c r="P28" s="43">
+        <f>N28*1000000</f>
+        <v>15000000</v>
+      </c>
+      <c r="Q28" s="43">
+        <f>P28/P29</f>
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P29">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>43</v>
       </c>
@@ -3934,21 +4033,33 @@
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
+    <row r="31" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="18"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
-    </row>
-    <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K31" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="L31" t="s">
+        <v>121</v>
+      </c>
+      <c r="N31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
+      <c r="K32" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16"/>
@@ -3992,7 +4103,8 @@
     <oddHeader>&amp;C&amp;9 &amp;K0B2E4FMacroeconomía · 200 FP</oddHeader>
     <oddFooter>&amp;C&amp;8 &amp;K4B5563Laboratorio · Del dato macroeconómico al mercado de un proyecto</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4014,7 +4126,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="16"/>
@@ -4262,7 +4374,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -4324,7 +4436,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -4414,7 +4526,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B1" s="16"/>
@@ -4466,7 +4578,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="33" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="16"/>
@@ -4496,7 +4608,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="16"/>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>B17</f>
         <v>7052.9348650000002</v>
       </c>
@@ -4525,7 +4637,7 @@
         <v>60</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="16"/>
@@ -4555,14 +4667,14 @@
         <v>60</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>B18</f>
         <v>2115.8804595000001</v>
       </c>
       <c r="G13" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="34" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="16"/>
@@ -4585,11 +4697,11 @@
         <f>Etapa1_Datos!F12</f>
         <v>7052.9348650000002</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="36" t="s">
         <v>72</v>
       </c>
       <c r="D17" s="16"/>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>B19</f>
         <v>528.97011487500004</v>
       </c>
@@ -4603,7 +4715,7 @@
         <f>B17*B7</f>
         <v>2115.8804595000001</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="36" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="16"/>
@@ -4616,7 +4728,7 @@
         <f>B18*B8</f>
         <v>528.97011487500004</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="16"/>
@@ -4633,7 +4745,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -4698,7 +4810,7 @@
       <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -4735,6 +4847,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A32:G35"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A2:H2"/>
@@ -4751,15 +4872,6 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A24:G29"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -4790,7 +4902,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="16"/>
@@ -4846,7 +4958,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="C8" s="4">
-        <f>Etapa3_Mercado!B19*B8</f>
+        <f>Etapa3_Mercado!$B$19*B8</f>
         <v>7.9345517231250007</v>
       </c>
       <c r="D8" s="12">
@@ -4926,7 +5038,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -4991,7 +5103,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -5063,7 +5175,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B1" s="16"/>
@@ -5202,7 +5314,7 @@
       <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -5260,7 +5372,7 @@
       <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -5326,7 +5438,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B1" s="16"/>
@@ -5604,7 +5716,7 @@
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
@@ -5646,7 +5758,7 @@
       <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -5688,7 +5800,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -5730,7 +5842,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="15"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -5805,6 +5917,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A43:H45"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A48:H50"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A54:H56"/>
@@ -5821,14 +5941,6 @@
     <mergeCell ref="A33:H35"/>
     <mergeCell ref="A38:H40"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A43:H45"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
